--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T12:50:06+00:00</t>
+    <t>2026-09-10T13:10:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:10:47+00:00</t>
+    <t>2026-09-10T13:32:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:32:54+00:00</t>
+    <t>2026-09-10T13:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:47:44+00:00</t>
+    <t>2026-09-10T16:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:40:19+00:00</t>
+    <t>2026-09-10T17:22:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:22:53+00:00</t>
+    <t>2026-09-10T17:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:39:40+00:00</t>
+    <t>2026-09-10T18:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T18:06:33+00:00</t>
+    <t>2026-09-11T06:33:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T06:33:50+00:00</t>
+    <t>2026-09-11T11:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:07:28+00:00</t>
+    <t>2026-09-11T11:48:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:48:22+00:00</t>
+    <t>2026-09-11T12:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:41:50+00:00</t>
+    <t>2026-09-11T12:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:56:10+00:00</t>
+    <t>2026-09-12T16:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T16:17:49+00:00</t>
+    <t>2026-09-12T17:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Ergebnis-ValueSet für die spezifische Mikroskopie: die semiquantitative Stufe, in der das im Code benannte Objekt gesehen wurde.</t>
+    <t>Mengen-ValueSet der Mikroskopie: die semiquantitative Stufe, in der ein mikroskopischer Befund gesehen wurde.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -142,30 +142,6 @@
   </si>
   <si>
     <t>Scanty</t>
-  </si>
-  <si>
-    <t>260413007</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>27863008</t>
-  </si>
-  <si>
-    <t>No organisms seen (finding)</t>
-  </si>
-  <si>
-    <t>52101004</t>
-  </si>
-  <si>
-    <t>Present</t>
-  </si>
-  <si>
-    <t>2667000</t>
-  </si>
-  <si>
-    <t>Absent</t>
   </si>
   <si>
     <t/>
@@ -438,7 +414,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -514,47 +490,15 @@
         <v>43</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T17:15:10+00:00</t>
+    <t>2026-09-12T20:14:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
